--- a/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>20321 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.1096</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.60711000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>331</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.1096</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.60711</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>20986 SAN MARTIN DE PORRAS / 676 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.1126</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.60558</v>
-      </c>
-      <c r="I3" t="n">
-        <v>995</v>
-      </c>
-      <c r="J3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.1126</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.60558</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>086</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.10754</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.59813</v>
-      </c>
-      <c r="I4" t="n">
-        <v>349</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.10754</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.59813</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>PEDRO E. PAULET</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.10467</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.60901</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1170</v>
-      </c>
-      <c r="J5" t="n">
-        <v>106</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.10467</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.60901</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>20325 SAN JOSE DE MANZANARES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.12904</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.61151</v>
-      </c>
-      <c r="I6" t="n">
-        <v>573</v>
-      </c>
-      <c r="J6" t="n">
-        <v>34</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.12904</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.61151</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>20318 JOSE ANTONIO MACNAMARA / 658</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.11726</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.61038000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>860</v>
-      </c>
-      <c r="J7" t="n">
-        <v>38</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.11726</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.61038</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>20321 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.10948</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.61174</v>
-      </c>
-      <c r="I8" t="n">
-        <v>516</v>
-      </c>
-      <c r="J8" t="n">
-        <v>27</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.10948</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.61174</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>20827 MERCEDES INDACOCHEA LOZANO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.121589</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.610642</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1451</v>
-      </c>
-      <c r="J9" t="n">
-        <v>97</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.121589</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.610642</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>20820 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.10603</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.60066999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>868</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.10603</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.60067</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>324 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.1222</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.61057</v>
-      </c>
-      <c r="I11" t="n">
-        <v>338</v>
-      </c>
-      <c r="J11" t="n">
-        <v>21</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.1222</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.61057</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>EUSEBIO ARRONIZ GOMEZ</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.10796</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.61363</v>
-      </c>
-      <c r="I12" t="n">
-        <v>251</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.10796</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.61363</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.106674</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.602446</v>
-      </c>
-      <c r="I13" t="n">
-        <v>391</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.106674</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.602446</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.10628</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.60630999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>218</v>
-      </c>
-      <c r="J14" t="n">
-        <v>35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.10628</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.60631</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SANTA ROSA MM.DD.</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.10796</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.61296</v>
-      </c>
-      <c r="I15" t="n">
-        <v>385</v>
-      </c>
-      <c r="J15" t="n">
-        <v>47</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.10796</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.61296</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.10453</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.60442</v>
-      </c>
-      <c r="I16" t="n">
-        <v>284</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.10453</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.60442</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>NUESTRA SEÑORA DE LA ANUNCIACION</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.10559</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.60303</v>
-      </c>
-      <c r="I17" t="n">
-        <v>433</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.10559</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.60303</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.10538</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.60973</v>
-      </c>
-      <c r="I18" t="n">
-        <v>706</v>
-      </c>
-      <c r="J18" t="n">
-        <v>43</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.10538</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.60973</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.11014</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.6084</v>
-      </c>
-      <c r="I19" t="n">
-        <v>204</v>
-      </c>
-      <c r="J19" t="n">
-        <v>13</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.11014</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.6084</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.1144</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.61100999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>972</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.1144</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.61101</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>DIVINO CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.11028</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.60874</v>
-      </c>
-      <c r="I21" t="n">
-        <v>331</v>
-      </c>
-      <c r="J21" t="n">
-        <v>32</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.11028</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.60874</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>NIKOLA TESLA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.109873</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.609917</v>
-      </c>
-      <c r="I22" t="n">
-        <v>309</v>
-      </c>
-      <c r="J22" t="n">
-        <v>21</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.109873</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.609917</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.10858</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.60630999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>498</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.10858</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.60631</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>20313 / 661</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.09656</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.62625</v>
-      </c>
-      <c r="I24" t="n">
-        <v>464</v>
-      </c>
-      <c r="J24" t="n">
-        <v>23</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.09656</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.62625</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>20320 DOMINGO MANDAMIENTO SIPAN</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.10491</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.6153</v>
-      </c>
-      <c r="I25" t="n">
-        <v>657</v>
-      </c>
-      <c r="J25" t="n">
-        <v>58</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.10491</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.6153</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.10339</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.59862</v>
-      </c>
-      <c r="I26" t="n">
-        <v>429</v>
-      </c>
-      <c r="J26" t="n">
-        <v>31</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.10339</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.59862</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>CORONEL PEDRO PORTILLO SILVA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.067427</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.60346</v>
-      </c>
-      <c r="I27" t="n">
-        <v>932</v>
-      </c>
-      <c r="J27" t="n">
-        <v>56</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.067427</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.60346</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>20335 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.06738</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.59905999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>827</v>
-      </c>
-      <c r="J28" t="n">
-        <v>44</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.06738</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.59906</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>20334 GENERALISIMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.06771</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.59851</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1162</v>
-      </c>
-      <c r="J29" t="n">
-        <v>60</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.06771</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.59851</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>20332 REINO DE SUECIA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.09646</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.41009</v>
-      </c>
-      <c r="I30" t="n">
-        <v>707</v>
-      </c>
-      <c r="J30" t="n">
-        <v>42</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.09646</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.41009</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>JULIO OCTAVIO REYES MOUNIER</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.185437</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.571535</v>
-      </c>
-      <c r="I31" t="n">
-        <v>627</v>
-      </c>
-      <c r="J31" t="n">
-        <v>31</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.185437</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.571535</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.2168</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.41289999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>427</v>
-      </c>
-      <c r="J32" t="n">
-        <v>17</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.2168</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.4129</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>FRAY MELCHOR APONTE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.0216</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.6374</v>
-      </c>
-      <c r="I33" t="n">
-        <v>562</v>
-      </c>
-      <c r="J33" t="n">
-        <v>44</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.0216</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.6374</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>20945</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-10.960294</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.64113</v>
-      </c>
-      <c r="I34" t="n">
-        <v>274</v>
-      </c>
-      <c r="J34" t="n">
-        <v>17</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-10.960294</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.64113</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.10732</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.60176</v>
-      </c>
-      <c r="I35" t="n">
-        <v>298</v>
-      </c>
-      <c r="J35" t="n">
-        <v>31</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.10732</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.60176</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>HAPPY CHILDREN</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.10627</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.59966</v>
-      </c>
-      <c r="I36" t="n">
-        <v>351</v>
-      </c>
-      <c r="J36" t="n">
-        <v>17</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.10627</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.59966</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>TRIOLET</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.06792</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.60039999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>408</v>
-      </c>
-      <c r="J37" t="n">
-        <v>28</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.06792</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.6004</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.2153</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.416</v>
-      </c>
-      <c r="I38" t="n">
-        <v>309</v>
-      </c>
-      <c r="J38" t="n">
-        <v>38</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.2153</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.416</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>INGENIERIA LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.11021</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.60382</v>
-      </c>
-      <c r="I39" t="n">
-        <v>245</v>
-      </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.11021</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.60382</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.10858</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.60630999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>400</v>
-      </c>
-      <c r="J40" t="n">
-        <v>26</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.10858</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.60631</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.12899</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.61014</v>
-      </c>
-      <c r="I41" t="n">
-        <v>231</v>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.12899</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.61014</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>CRAMER</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.10728</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.60048999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>454</v>
-      </c>
-      <c r="J42" t="n">
-        <v>30</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.10728</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.60049</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.106674</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.602446</v>
-      </c>
-      <c r="I43" t="n">
-        <v>301</v>
-      </c>
-      <c r="J43" t="n">
-        <v>18</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.106674</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.602446</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>INNOVA SCHOOLS - HUACHO</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.12159</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.60444</v>
-      </c>
-      <c r="I44" t="n">
-        <v>862</v>
-      </c>
-      <c r="J44" t="n">
-        <v>47</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.12159</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.60444</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>COLUMBIA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.11397</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.60332</v>
-      </c>
-      <c r="I45" t="n">
-        <v>445</v>
-      </c>
-      <c r="J45" t="n">
-        <v>32</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.11397</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.60332</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>EUSEBIO ARRONIZ SCHOOL</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.109811</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.605171</v>
-      </c>
-      <c r="I46" t="n">
-        <v>392</v>
-      </c>
-      <c r="J46" t="n">
-        <v>22</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.109811</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.605171</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>ELITE SCHOOL</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.108076</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.603312</v>
-      </c>
-      <c r="I47" t="n">
-        <v>637</v>
-      </c>
-      <c r="J47" t="n">
-        <v>27</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.108076</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.603312</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>ELITE SCHOOL</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.107978</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.60317499999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>395</v>
-      </c>
-      <c r="J48" t="n">
-        <v>16</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.107978</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.603175</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>GALILEO - HUACHO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.107895</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.605062</v>
-      </c>
-      <c r="I49" t="n">
-        <v>396</v>
-      </c>
-      <c r="J49" t="n">
-        <v>22</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.107895</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.605062</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>340523</t>
+          <t>359541</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20321 SANTA ROSA</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.1096</t>
+          <t>-11.10858</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.60711</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>498</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>358990</t>
+          <t>359013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20986 SAN MARTIN DE PORRAS / 676 SAN MARTIN DE PORRAS</t>
+          <t>PEDRO E. PAULET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.1126</t>
+          <t>-11.10467</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.60558</t>
+          <t>-77.60901</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>359008</t>
+          <t>359174</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>EUSEBIO ARRONIZ GOMEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.10754</t>
+          <t>-11.10796</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.59813</t>
+          <t>-77.61363</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>359013</t>
+          <t>359334</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEDRO E. PAULET</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.10467</t>
+          <t>-11.10453</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.60901</t>
+          <t>-77.60442</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>359027</t>
+          <t>359490</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20325 SAN JOSE DE MANZANARES</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.12904</t>
+          <t>-11.11014</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.61151</t>
+          <t>-77.6084</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>359032</t>
+          <t>732385</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20318 JOSE ANTONIO MACNAMARA / 658</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.11726</t>
+          <t>-11.12899</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.61038</t>
+          <t>-77.61014</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>359070</t>
+          <t>359008</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20321 SANTA ROSA</t>
+          <t>086</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.10948</t>
+          <t>-11.10754</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.61174</t>
+          <t>-77.59813</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>359112</t>
+          <t>865021</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20827 MERCEDES INDACOCHEA LOZANO</t>
+          <t>ELITE SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.121589</t>
+          <t>-11.107978</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.610642</t>
+          <t>-77.603175</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>395</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>359126</t>
+          <t>361134</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20820 NUESTRA SEÑORA DE FATIMA</t>
+          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.10603</t>
+          <t>-11.2168</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.60067</t>
+          <t>-77.4129</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>427</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>359145</t>
+          <t>361327</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>324 SANTISIMA NIÑA MARIA</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.1222</t>
+          <t>-10.960294</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.61057</t>
+          <t>-77.64113</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>359174</t>
+          <t>578505</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EUSEBIO ARRONIZ GOMEZ</t>
+          <t>HAPPY CHILDREN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.10796</t>
+          <t>-11.10627</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.61363</t>
+          <t>-77.59966</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>359230</t>
+          <t>732639</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>359249</t>
+          <t>340523</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>20321 SANTA ROSA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.10628</t>
+          <t>-11.1096</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>-77.60711</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>359268</t>
+          <t>359145</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA ROSA MM.DD.</t>
+          <t>324 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.10796</t>
+          <t>-11.1222</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.61296</t>
+          <t>-77.61057</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>359334</t>
+          <t>359536</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>NIKOLA TESLA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.10453</t>
+          <t>-11.109873</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.60442</t>
+          <t>-77.609917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>359414</t>
+          <t>672838</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ANUNCIACION</t>
+          <t>INGENIERIA LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.10559</t>
+          <t>-11.11021</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.60303</t>
+          <t>-77.60382</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>359485</t>
+          <t>864446</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>EUSEBIO ARRONIZ SCHOOL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.10538</t>
+          <t>-11.109811</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.60973</t>
+          <t>-77.605171</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>359490</t>
+          <t>904414</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>GALILEO - HUACHO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.11014</t>
+          <t>-11.107895</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.6084</t>
+          <t>-77.605062</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>359503</t>
+          <t>359843</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN JOSE HERMANOS MARISTAS</t>
+          <t>20313 / 661</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.1144</t>
+          <t>-11.09656</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.61101</t>
+          <t>-77.62625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>464</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>359517</t>
+          <t>359414</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS SCHOOL</t>
+          <t>NUESTRA SEÑORA DE LA ANUNCIACION</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.11028</t>
+          <t>-11.10559</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.60874</t>
+          <t>-77.60303</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>359536</t>
+          <t>732205</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NIKOLA TESLA</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.109873</t>
+          <t>-11.10858</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.609917</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>359541</t>
+          <t>359070</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>20321 SANTA ROSA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.10858</t>
+          <t>-11.10948</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>-77.61174</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>359843</t>
+          <t>865016</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20313 / 661</t>
+          <t>ELITE SCHOOL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.09656</t>
+          <t>-11.108076</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.62625</t>
+          <t>-77.603312</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>637</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>360021</t>
+          <t>359230</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20320 DOMINGO MANDAMIENTO SIPAN</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.10491</t>
+          <t>-11.106674</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.6153</t>
+          <t>-77.602446</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>360139</t>
+          <t>602077</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>TRIOLET</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.10339</t>
+          <t>-11.06792</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.59862</t>
+          <t>-77.6004</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>360200</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CORONEL PEDRO PORTILLO SILVA</t>
+          <t>CRAMER</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.067427</t>
+          <t>-11.10728</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.60346</t>
+          <t>-77.60049</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>454</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>360238</t>
+          <t>360139</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20335 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.06738</t>
+          <t>-11.10339</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.59906</t>
+          <t>-77.59862</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>360276</t>
+          <t>360813</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20334 GENERALISIMO DON JOSE DE SAN MARTIN</t>
+          <t>JULIO OCTAVIO REYES MOUNIER</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.06771</t>
+          <t>-11.185437</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.59851</t>
+          <t>-77.571535</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>627</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>360295</t>
+          <t>505726</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20332 REINO DE SUECIA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.09646</t>
+          <t>-11.10732</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.41009</t>
+          <t>-77.60176</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>360813</t>
+          <t>359517</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JULIO OCTAVIO REYES MOUNIER</t>
+          <t>DIVINO CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.185437</t>
+          <t>-11.11028</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.571535</t>
+          <t>-77.60874</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>361134</t>
+          <t>863036</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>COLUMBIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.2168</t>
+          <t>-11.11397</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.4129</t>
+          <t>-77.60332</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>445</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>361285</t>
+          <t>359027</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FRAY MELCHOR APONTE</t>
+          <t>20325 SAN JOSE DE MANZANARES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.0216</t>
+          <t>-11.12904</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.6374</t>
+          <t>-77.61151</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>573</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>361327</t>
+          <t>359249</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-10.960294</t>
+          <t>-11.10628</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.64113</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>505726</t>
+          <t>359032</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>20318 JOSE ANTONIO MACNAMARA / 658</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.10732</t>
+          <t>-11.11726</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.60176</t>
+          <t>-77.61038</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>860</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>578505</t>
+          <t>359503</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HAPPY CHILDREN</t>
+          <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.10627</t>
+          <t>-11.1144</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.59966</t>
+          <t>-77.61101</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>972</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>602077</t>
+          <t>626592</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRIOLET</t>
+          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.06792</t>
+          <t>-11.2153</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.6004</t>
+          <t>-77.416</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>626592</t>
+          <t>359126</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>20820 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.2153</t>
+          <t>-11.10603</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.416</t>
+          <t>-77.60067</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>868</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>672838</t>
+          <t>360295</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INGENIERIA LEONCIO PRADO</t>
+          <t>20332 REINO DE SUECIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.11021</t>
+          <t>-11.09646</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.60382</t>
+          <t>-77.41009</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>707</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>732205</t>
+          <t>359485</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.10858</t>
+          <t>-11.10538</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>-77.60973</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>706</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>732385</t>
+          <t>360238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>20335 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.12899</t>
+          <t>-11.06738</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.61014</t>
+          <t>-77.59906</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>827</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>361285</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CRAMER</t>
+          <t>FRAY MELCHOR APONTE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.10728</t>
+          <t>-11.0216</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.60049</t>
+          <t>-77.6374</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>732639</t>
+          <t>359268</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>SANTA ROSA MM.DD.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.106674</t>
+          <t>-11.10796</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.602446</t>
+          <t>-77.61296</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>385</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>863036</t>
+          <t>358990</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>COLUMBIA</t>
+          <t>20986 SAN MARTIN DE PORRAS / 676 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.11397</t>
+          <t>-11.1126</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.60332</t>
+          <t>-77.60558</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>995</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>864446</t>
+          <t>360200</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EUSEBIO ARRONIZ SCHOOL</t>
+          <t>CORONEL PEDRO PORTILLO SILVA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.109811</t>
+          <t>-11.067427</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.605171</t>
+          <t>-77.60346</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>932</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>865016</t>
+          <t>360021</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ELITE SCHOOL</t>
+          <t>20320 DOMINGO MANDAMIENTO SIPAN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.108076</t>
+          <t>-11.10491</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.603312</t>
+          <t>-77.6153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>657</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>865021</t>
+          <t>360276</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ELITE SCHOOL</t>
+          <t>20334 GENERALISIMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.107978</t>
+          <t>-11.06771</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.603175</t>
+          <t>-77.59851</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>904414</t>
+          <t>359112</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GALILEO - HUACHO</t>
+          <t>20827 MERCEDES INDACOCHEA LOZANO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.107895</t>
+          <t>-11.121589</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.605062</t>
+          <t>-77.610642</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>359541</t>
+          <t>904414</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>GALILEO - HUACHO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.10858</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>-11.107895</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.605062</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>359013</t>
+          <t>865021</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEDRO E. PAULET</t>
+          <t>ELITE SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.10467</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.60901</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>-11.107978</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-77.603175</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>359174</t>
+          <t>865016</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EUSEBIO ARRONIZ GOMEZ</t>
+          <t>ELITE SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.10796</t>
+          <t>637</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.61363</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-11.108076</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.603312</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>359334</t>
+          <t>864446</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>EUSEBIO ARRONIZ SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.10453</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.60442</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-11.109811</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.605171</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>359490</t>
+          <t>863036</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>COLUMBIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.11014</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.6084</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-11.11397</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.60332</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>732385</t>
+          <t>748701</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>INNOVA SCHOOLS - HUACHO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.12899</t>
+          <t>862</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.61014</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.12159</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.60444</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>359008</t>
+          <t>732639</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.10754</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.59813</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-11.106674</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.602446</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>865021</t>
+          <t>732516</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ELITE SCHOOL</t>
+          <t>CRAMER</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.107978</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.603175</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>-11.10728</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.60049</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>361134</t>
+          <t>732385</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.2168</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.4129</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>-11.12899</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.61014</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>361327</t>
+          <t>732205</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-10.960294</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.64113</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-11.10858</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>578505</t>
+          <t>672838</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HAPPY CHILDREN</t>
+          <t>INGENIERIA LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.10627</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.59966</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-11.11021</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.60382</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>732639</t>
+          <t>626592</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.106674</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.602446</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-11.2153</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.416</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>340523</t>
+          <t>602077</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20321 SANTA ROSA</t>
+          <t>TRIOLET</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.1096</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.60711</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-11.06792</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.6004</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>359145</t>
+          <t>578505</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>324 SANTISIMA NIÑA MARIA</t>
+          <t>HAPPY CHILDREN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.1222</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.61057</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-11.10627</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.59966</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>359536</t>
+          <t>505726</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NIKOLA TESLA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.109873</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.609917</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-11.10732</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.60176</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>672838</t>
+          <t>361327</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>INGENIERIA LEONCIO PRADO</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.11021</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.60382</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-10.960294</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.64113</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>864446</t>
+          <t>361285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EUSEBIO ARRONIZ SCHOOL</t>
+          <t>FRAY MELCHOR APONTE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.109811</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.605171</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-11.0216</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.6374</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>904414</t>
+          <t>361134</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GALILEO - HUACHO</t>
+          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.107895</t>
+          <t>427</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.605062</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-11.2168</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.4129</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>359843</t>
+          <t>360813</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20313 / 661</t>
+          <t>JULIO OCTAVIO REYES MOUNIER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.09656</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.62625</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>-11.185437</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.571535</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>359414</t>
+          <t>360295</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ANUNCIACION</t>
+          <t>20332 REINO DE SUECIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.10559</t>
+          <t>707</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.60303</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-11.09646</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.41009</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>732205</t>
+          <t>360276</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>20334 GENERALISIMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.10858</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-11.06771</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.59851</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>359070</t>
+          <t>360238</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20321 SANTA ROSA</t>
+          <t>20335 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.10948</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.61174</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-11.06738</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.59906</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>865016</t>
+          <t>360200</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ELITE SCHOOL</t>
+          <t>CORONEL PEDRO PORTILLO SILVA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.108076</t>
+          <t>932</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.603312</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>-11.067427</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.60346</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>359230</t>
+          <t>360139</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.106674</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.602446</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-11.10339</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.59862</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>602077</t>
+          <t>360021</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRIOLET</t>
+          <t>20320 DOMINGO MANDAMIENTO SIPAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.06792</t>
+          <t>657</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.6004</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-11.10491</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.6153</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>732516</t>
+          <t>359843</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CRAMER</t>
+          <t>20313 / 661</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.10728</t>
+          <t>464</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.60049</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>-11.09656</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.62625</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>360139</t>
+          <t>359541</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.10339</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.59862</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-11.10858</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>360813</t>
+          <t>359536</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JULIO OCTAVIO REYES MOUNIER</t>
+          <t>NIKOLA TESLA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.185437</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.571535</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>-11.109873</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.609917</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>505726</t>
+          <t>359517</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>DIVINO CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.10732</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.60176</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-11.11028</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.60874</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>359517</t>
+          <t>359503</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS SCHOOL</t>
+          <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.11028</t>
+          <t>972</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.60874</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-11.1144</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.61101</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>863036</t>
+          <t>359490</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>COLUMBIA</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.11397</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.60332</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-11.11014</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.6084</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>359027</t>
+          <t>359485</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20325 SAN JOSE DE MANZANARES</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.12904</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.61151</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>-11.10538</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.60973</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>359249</t>
+          <t>359414</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>NUESTRA SEÑORA DE LA ANUNCIACION</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.10628</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.60631</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-11.10559</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.60303</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>359032</t>
+          <t>359334</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20318 JOSE ANTONIO MACNAMARA / 658</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.11726</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.61038</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>-11.10453</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.60442</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>359503</t>
+          <t>359268</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN JOSE HERMANOS MARISTAS</t>
+          <t>SANTA ROSA MM.DD.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.1144</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.61101</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>-11.10796</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.61296</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>626592</t>
+          <t>359249</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.2153</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.416</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-11.10628</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.60631</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>359126</t>
+          <t>359230</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20820 NUESTRA SEÑORA DE FATIMA</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.10603</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.60067</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>-11.106674</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.602446</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>360295</t>
+          <t>359174</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20332 REINO DE SUECIA</t>
+          <t>EUSEBIO ARRONIZ GOMEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.09646</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.41009</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>-11.10796</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.61363</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>359485</t>
+          <t>359145</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>324 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.10538</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.60973</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>-11.1222</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.61057</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>360238</t>
+          <t>359126</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20335 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>20820 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.06738</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.59906</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>-11.10603</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.60067</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>361285</t>
+          <t>359112</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FRAY MELCHOR APONTE</t>
+          <t>20827 MERCEDES INDACOCHEA LOZANO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.0216</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.6374</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>-11.121589</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.610642</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>359268</t>
+          <t>359070</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTA ROSA MM.DD.</t>
+          <t>20321 SANTA ROSA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.10796</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.61296</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>-11.10948</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.61174</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>748701</t>
+          <t>359032</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - HUACHO</t>
+          <t>20318 JOSE ANTONIO MACNAMARA / 658</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.12159</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.60444</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>-11.11726</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.61038</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>358990</t>
+          <t>359027</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20986 SAN MARTIN DE PORRAS / 676 SAN MARTIN DE PORRAS</t>
+          <t>20325 SAN JOSE DE MANZANARES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.1126</t>
+          <t>573</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.60558</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>-11.12904</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.61151</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>360200</t>
+          <t>359013</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CORONEL PEDRO PORTILLO SILVA</t>
+          <t>PEDRO E. PAULET</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.067427</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.60346</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>-11.10467</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.60901</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>360021</t>
+          <t>359008</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20320 DOMINGO MANDAMIENTO SIPAN</t>
+          <t>086</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.10491</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.6153</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>-11.10754</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.59813</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>360276</t>
+          <t>358990</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20334 GENERALISIMO DON JOSE DE SAN MARTIN</t>
+          <t>20986 SAN MARTIN DE PORRAS / 676 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.06771</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.59851</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>-11.1126</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-77.60558</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>359112</t>
+          <t>340523</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20827 MERCEDES INDACOCHEA LOZANO</t>
+          <t>20321 SANTA ROSA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.121589</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.610642</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>-11.1096</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-77.60711</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUAURA-HUACHO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
